--- a/docs/build/lakeshore-enterprise-context/source/09_servicenow_support_workload/enhancement_backlog.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/09_servicenow_support_workload/enhancement_backlog.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -501,15 +501,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,11 +531,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Azure AD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -561,15 +561,15 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -625,11 +625,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -651,15 +651,15 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -711,15 +711,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -745,11 +745,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -771,15 +771,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -801,15 +801,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -831,15 +831,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -861,15 +861,15 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -895,11 +895,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -921,11 +921,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -951,15 +951,15 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -981,15 +981,15 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1011,15 +1011,15 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1041,15 +1041,15 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1071,15 +1071,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1131,15 +1131,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>SAP ECC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1161,11 +1161,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1221,15 +1221,15 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1251,15 +1251,15 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1311,15 +1311,15 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1341,15 +1341,15 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1371,15 +1371,15 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1405,11 +1405,11 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1435,11 +1435,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1465,11 +1465,11 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1491,15 +1491,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1525,11 +1525,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1551,15 +1551,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1585,11 +1585,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1611,15 +1611,15 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1641,15 +1641,15 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>SAP ECC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1701,11 +1701,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>SAP ECC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1765,11 +1765,11 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1791,15 +1791,15 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -1821,11 +1821,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1881,15 +1881,15 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1915,11 +1915,11 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1945,11 +1945,11 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1975,11 +1975,11 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>SAP ECC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2005,11 +2005,11 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2031,15 +2031,15 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2061,15 +2061,15 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Azure AD</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2095,11 +2095,11 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>SAP ECC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2121,15 +2121,15 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2151,11 +2151,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2185,11 +2185,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2215,11 +2215,11 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2241,11 +2241,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2271,15 +2271,15 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Azure AD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2301,11 +2301,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2335,11 +2335,11 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Azure AD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2361,15 +2361,15 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2391,11 +2391,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2421,15 +2421,15 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2455,11 +2455,11 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2481,15 +2481,15 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2515,11 +2515,11 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2541,15 +2541,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Azure AD</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2571,15 +2571,15 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2631,15 +2631,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2661,11 +2661,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2691,15 +2691,15 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -2721,15 +2721,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2751,15 +2751,15 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2781,11 +2781,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2811,15 +2811,15 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2841,15 +2841,15 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2871,11 +2871,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2901,15 +2901,15 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Azure AD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2935,11 +2935,11 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2961,15 +2961,15 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -3115,11 +3115,11 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Azure AD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3145,11 +3145,11 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3171,15 +3171,15 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3201,11 +3201,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3231,15 +3231,15 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Azure AD</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3261,11 +3261,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3351,15 +3351,15 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3385,11 +3385,11 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3411,11 +3411,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>SAP ECC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3445,11 +3445,11 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3471,15 +3471,15 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3531,11 +3531,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3561,15 +3561,15 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Scoped</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3591,15 +3591,15 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Azure AD</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3621,15 +3621,15 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3681,15 +3681,15 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3715,11 +3715,11 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3741,15 +3741,15 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3771,15 +3771,15 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3801,15 +3801,15 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SAP ECC</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Dev</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3861,11 +3861,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3891,15 +3891,15 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3921,11 +3921,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -3951,11 +3951,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>SAP ECC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3985,11 +3985,11 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -4011,15 +4011,15 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>In Dev</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4041,15 +4041,15 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Scoped</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4071,15 +4071,15 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
